--- a/research/traditional_assets/database/data/pakistan/pakistan_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0493</v>
+        <v>0.0394</v>
       </c>
       <c r="E2">
-        <v>0.149</v>
+        <v>-0.027</v>
       </c>
       <c r="G2">
-        <v>0.4488948425987943</v>
+        <v>0.1718554078744671</v>
       </c>
       <c r="H2">
-        <v>0.4487608841259209</v>
+        <v>0.1718374950739799</v>
       </c>
       <c r="I2">
-        <v>0.510649698593436</v>
+        <v>0.1048973596532082</v>
       </c>
       <c r="J2">
-        <v>0.4224624129141529</v>
+        <v>0.08397534695214923</v>
       </c>
       <c r="K2">
-        <v>5.947</v>
+        <v>4.528</v>
       </c>
       <c r="L2">
-        <v>0.3983255190890824</v>
+        <v>0.08110916060616916</v>
       </c>
       <c r="M2">
-        <v>4.058</v>
+        <v>4.376</v>
       </c>
       <c r="N2">
-        <v>0.1219350961538462</v>
+        <v>0.1792487609060746</v>
       </c>
       <c r="O2">
-        <v>0.6823608542122078</v>
+        <v>0.9664310954063606</v>
       </c>
       <c r="P2">
-        <v>4.058</v>
+        <v>4.376</v>
       </c>
       <c r="Q2">
-        <v>0.1219350961538462</v>
+        <v>0.1792487609060746</v>
       </c>
       <c r="R2">
-        <v>0.6823608542122078</v>
+        <v>0.9664310954063606</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.706</v>
+        <v>3.025</v>
       </c>
       <c r="V2">
-        <v>0.1113581730769231</v>
+        <v>0.1239093925367632</v>
       </c>
       <c r="W2">
-        <v>0.02245886834835929</v>
+        <v>0.004411764705882353</v>
       </c>
       <c r="X2">
-        <v>0.09063532077991254</v>
+        <v>0.1479271621937633</v>
       </c>
       <c r="Y2">
-        <v>-0.06817645243155326</v>
+        <v>-0.1435153974878809</v>
       </c>
       <c r="Z2">
-        <v>0.4945018547959725</v>
+        <v>1.350966773951553</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09034549139118583</v>
+        <v>0.1469033425597125</v>
       </c>
       <c r="AC2">
-        <v>-0.09014349724412796</v>
+        <v>-0.1461009939540135</v>
       </c>
       <c r="AD2">
-        <v>3.194</v>
+        <v>8.863</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.194</v>
+        <v>8.863</v>
       </c>
       <c r="AG2">
-        <v>-0.512</v>
+        <v>5.837999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.08756922739485661</v>
+        <v>0.2663481187642746</v>
       </c>
       <c r="AI2">
-        <v>0.07018237749945067</v>
+        <v>0.2065197129275794</v>
       </c>
       <c r="AJ2">
-        <v>-0.015625</v>
+        <v>0.1929853558560047</v>
       </c>
       <c r="AK2">
-        <v>-0.01224763180556885</v>
+        <v>0.1463488004813115</v>
       </c>
       <c r="AL2">
-        <v>0.454</v>
+        <v>0.448</v>
       </c>
       <c r="AM2">
-        <v>0.443</v>
+        <v>0.2919999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.412981639513835</v>
+        <v>1.491083445491252</v>
       </c>
       <c r="AO2">
-        <v>16.79295154185022</v>
+        <v>13.07142857142857</v>
       </c>
       <c r="AP2">
-        <v>-0.06620118955262477</v>
+        <v>0.9821668909825032</v>
       </c>
       <c r="AQ2">
-        <v>17.2099322799097</v>
+        <v>20.05479452054795</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cyan Limited (KASE:CYAN)</t>
+          <t>Globe Residency REIT (KASE:GRR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,122 +721,95 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.143</v>
-      </c>
-      <c r="E3">
-        <v>0.149</v>
-      </c>
       <c r="G3">
-        <v>0.4277124183006535</v>
+        <v>0.1583665338645418</v>
       </c>
       <c r="H3">
-        <v>0.4274509803921568</v>
+        <v>0.1583665338645418</v>
       </c>
       <c r="I3">
-        <v>0.8130718954248365</v>
+        <v>0.1583665338645418</v>
       </c>
       <c r="J3">
-        <v>0.6635101755306358</v>
+        <v>0.1314815089086035</v>
       </c>
       <c r="K3">
-        <v>4.88</v>
+        <v>6.7</v>
       </c>
       <c r="L3">
-        <v>0.6379084967320261</v>
+        <v>0.1334661354581673</v>
       </c>
       <c r="M3">
-        <v>1.8</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1512605042016807</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.3688524590163935</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>1.8</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1512605042016807</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3688524590163935</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0.036</v>
+        <v>0.136</v>
       </c>
       <c r="V3">
-        <v>0.003025210084033613</v>
-      </c>
-      <c r="W3">
-        <v>0.4170940170940171</v>
+        <v>0.02048192771084338</v>
       </c>
       <c r="X3">
-        <v>0.09632228872310244</v>
-      </c>
-      <c r="Y3">
-        <v>0.3207717283709147</v>
-      </c>
-      <c r="Z3">
-        <v>0.5012777668566936</v>
-      </c>
-      <c r="AA3">
-        <v>0.3326028990766899</v>
+        <v>0.2164332403374553</v>
       </c>
       <c r="AB3">
-        <v>0.09245943315007915</v>
-      </c>
-      <c r="AC3">
-        <v>0.2401434659266108</v>
+        <v>0.1638489810418891</v>
       </c>
       <c r="AD3">
-        <v>1.38</v>
+        <v>6.13</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.38</v>
+        <v>6.13</v>
       </c>
       <c r="AG3">
-        <v>1.344</v>
+        <v>5.994</v>
       </c>
       <c r="AH3">
-        <v>0.1039156626506024</v>
+        <v>0.4800313234142521</v>
       </c>
       <c r="AI3">
-        <v>0.0994236311239193</v>
+        <v>0.4588323353293413</v>
       </c>
       <c r="AJ3">
-        <v>0.1014799154334038</v>
+        <v>0.4744340668038626</v>
       </c>
       <c r="AK3">
-        <v>0.097081768275065</v>
+        <v>0.4532667876588021</v>
       </c>
       <c r="AL3">
-        <v>0.196</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.196</v>
+        <v>-0.147</v>
       </c>
       <c r="AN3">
-        <v>0.2211538461538461</v>
-      </c>
-      <c r="AO3">
-        <v>31.73469387755102</v>
+        <v>0.771069182389937</v>
       </c>
       <c r="AP3">
-        <v>0.2153846153846154</v>
+        <v>0.7539622641509434</v>
       </c>
       <c r="AQ3">
-        <v>31.73469387755102</v>
+        <v>-54.08163265306123</v>
       </c>
     </row>
     <row r="4">
@@ -856,46 +829,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0532</v>
+        <v>0.0349</v>
       </c>
       <c r="E4">
-        <v>0.07919999999999999</v>
+        <v>-0.027</v>
       </c>
       <c r="G4">
-        <v>0.5694200351493849</v>
+        <v>0.3759213759213759</v>
       </c>
       <c r="H4">
-        <v>0.5694200351493849</v>
+        <v>0.3759213759213759</v>
       </c>
       <c r="I4">
-        <v>0.4622144112478031</v>
+        <v>0.3292383292383292</v>
       </c>
       <c r="J4">
-        <v>0.3443318210923556</v>
+        <v>0.2000372273099546</v>
       </c>
       <c r="K4">
-        <v>1.92</v>
+        <v>0.8</v>
       </c>
       <c r="L4">
-        <v>0.3374340949033391</v>
+        <v>0.1965601965601965</v>
       </c>
       <c r="M4">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="N4">
-        <v>0.1328671328671329</v>
+        <v>0.2205882352941176</v>
       </c>
       <c r="O4">
-        <v>0.9895833333333334</v>
+        <v>1.875</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q4">
-        <v>0.1328671328671329</v>
+        <v>0.2205882352941176</v>
       </c>
       <c r="R4">
-        <v>0.9895833333333334</v>
+        <v>1.875</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +877,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.266</v>
+        <v>0.171</v>
       </c>
       <c r="V4">
-        <v>0.0186013986013986</v>
+        <v>0.02514705882352941</v>
       </c>
       <c r="W4">
-        <v>0.192</v>
+        <v>0.08179959100204499</v>
       </c>
       <c r="X4">
-        <v>0.09112714431569713</v>
+        <v>0.1479271621937633</v>
       </c>
       <c r="Y4">
-        <v>0.1008728556843029</v>
+        <v>-0.06612757119171826</v>
       </c>
       <c r="Z4">
-        <v>0.5886003930898935</v>
+        <v>0.4377756265461978</v>
       </c>
       <c r="AA4">
-        <v>0.2026738452483194</v>
+        <v>0.08757142251817956</v>
       </c>
       <c r="AB4">
-        <v>0.0905474855382437</v>
+        <v>0.1469033425597125</v>
       </c>
       <c r="AC4">
-        <v>0.1121263597100757</v>
+        <v>-0.05933192004153295</v>
       </c>
       <c r="AD4">
-        <v>0.264</v>
+        <v>0.163</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.264</v>
+        <v>0.163</v>
       </c>
       <c r="AG4">
-        <v>-0.002000000000000002</v>
+        <v>-0.008000000000000007</v>
       </c>
       <c r="AH4">
-        <v>0.01812688821752266</v>
+        <v>0.02340944994973431</v>
       </c>
       <c r="AI4">
-        <v>0.02628434886499403</v>
+        <v>0.02406614498745017</v>
       </c>
       <c r="AJ4">
-        <v>-0.0001398797034550288</v>
+        <v>-0.001177856301531214</v>
       </c>
       <c r="AK4">
-        <v>-0.0002045408058907754</v>
+        <v>-0.001211754013935172</v>
       </c>
       <c r="AL4">
-        <v>0.041</v>
+        <v>0.023</v>
       </c>
       <c r="AM4">
-        <v>0.038</v>
+        <v>0.017</v>
       </c>
       <c r="AN4">
-        <v>0.09741697416974171</v>
+        <v>0.1164285714285714</v>
       </c>
       <c r="AO4">
-        <v>64.14634146341463</v>
+        <v>58.2608695652174</v>
       </c>
       <c r="AP4">
-        <v>-0.0007380073800738014</v>
+        <v>-0.005714285714285719</v>
       </c>
       <c r="AQ4">
-        <v>69.21052631578948</v>
+        <v>78.82352941176471</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sindh Modaraba (KASE:SINDM)</t>
+          <t>786 Investment Limited (KASE:786)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,79 +963,76 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0493</v>
+        <v>0.268</v>
       </c>
       <c r="E5">
-        <v>0.294</v>
+        <v>-0.528</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.2323943661971831</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.2323943661971831</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.1901408450704226</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.09507042253521128</v>
       </c>
       <c r="K5">
-        <v>0.419</v>
+        <v>0.006</v>
       </c>
       <c r="L5">
-        <v>0.5771349862258953</v>
+        <v>0.04225352112676057</v>
       </c>
       <c r="M5">
-        <v>0.356</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.1883597883597884</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.8496420047732697</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.356</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.1883597883597884</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.8496420047732697</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>3.25</v>
+        <v>0.003</v>
       </c>
       <c r="V5">
-        <v>1.71957671957672</v>
+        <v>0.00909090909090909</v>
       </c>
       <c r="W5">
-        <v>0.04419831223628692</v>
+        <v>0.004411764705882353</v>
       </c>
       <c r="X5">
-        <v>0.09014349724412796</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="Y5">
-        <v>-0.04594518500784104</v>
+        <v>-0.1416892292481312</v>
       </c>
       <c r="Z5">
-        <v>0.1861538461538461</v>
+        <v>0.1094834232845027</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.01040863531225906</v>
       </c>
       <c r="AB5">
-        <v>0.09014349724412796</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="AC5">
-        <v>-0.09014349724412796</v>
+        <v>-0.1356923586417545</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1074,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-3.25</v>
+        <v>-0.003</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1083,16 +1053,28 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>2.389705882352941</v>
+        <v>-0.009174311926605505</v>
       </c>
       <c r="AK5">
-        <v>-0.531045751633987</v>
+        <v>-0.002949852507374631</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.009999999999999998</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>2.076923076923077</v>
+      </c>
+      <c r="AP5">
+        <v>-0.09375</v>
+      </c>
+      <c r="AQ5">
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unicap Modaraba (KASE:UCAPM)</t>
+          <t>Sindh Modaraba (KASE:SINDM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1111,56 +1093,80 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.04389999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.174</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
       <c r="K6">
-        <v>-0.013</v>
+        <v>0.345</v>
+      </c>
+      <c r="L6">
+        <v>0.4451612903225806</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.196</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.1410071942446043</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.5681159420289855</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>0.196</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.1410071942446043</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>0.5681159420289855</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.856115107913669</v>
       </c>
       <c r="W6">
-        <v>-0.07103825136612021</v>
+        <v>0.0368196371398079</v>
       </c>
       <c r="X6">
-        <v>0.09014349724412796</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="Y6">
-        <v>-0.1611817486102482</v>
+        <v>-0.1092813568142056</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>0.1266339869281046</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.09014349724412796</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="AC6">
-        <v>-0.09014349724412796</v>
+        <v>-0.1461009939540135</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1172,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>-2.58</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1181,10 +1187,10 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>2.168067226890756</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>-0.5695364238410596</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>786 Investment Limited (KASE:786)</t>
+          <t>Unicap Modaraba (KASE:UCAPM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1209,26 +1215,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.00676</v>
-      </c>
       <c r="G7">
-        <v>-0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-1.303030303030303</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>-0.6515151515151514</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="L7">
-        <v>0.01515151515151515</v>
+        <v>-0.1</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1237,7 +1240,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1246,37 +1249,37 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>0.114963503649635</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>0.0007194244604316547</v>
+        <v>-0.005376344086021506</v>
       </c>
       <c r="X7">
-        <v>0.09014349724412796</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="Y7">
-        <v>-0.0894240727836963</v>
+        <v>-0.151477338040035</v>
       </c>
       <c r="Z7">
-        <v>0.05588484335309061</v>
+        <v>0.05376344086021505</v>
       </c>
       <c r="AA7">
-        <v>-0.03640982218458933</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.09014349724412796</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="AC7">
-        <v>-0.1265533194287173</v>
+        <v>-0.1461009939540135</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1288,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.063</v>
+        <v>0</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1297,28 +1300,16 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.1298969072164948</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>-0.04857363145720894</v>
+        <v>0</v>
       </c>
       <c r="AL7">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>0.004</v>
-      </c>
-      <c r="AN7">
-        <v>-0</v>
-      </c>
-      <c r="AO7">
-        <v>-7.166666666666666</v>
-      </c>
-      <c r="AP7">
-        <v>0.8289473684210527</v>
-      </c>
-      <c r="AQ7">
-        <v>-21.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1338,103 +1329,228 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.122</v>
+        <v>-0.219</v>
       </c>
       <c r="G8">
-        <v>0.2932330827067669</v>
+        <v>-2.1939586645469</v>
       </c>
       <c r="H8">
-        <v>0.2932330827067669</v>
+        <v>-2.1939586645469</v>
       </c>
       <c r="I8">
-        <v>-1.428571428571428</v>
+        <v>-1.448330683624801</v>
       </c>
       <c r="J8">
-        <v>-1.428571428571428</v>
+        <v>-1.448330683624801</v>
       </c>
       <c r="K8">
-        <v>-1.26</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="L8">
-        <v>-1.578947368421053</v>
+        <v>-1.481717011128776</v>
       </c>
       <c r="M8">
-        <v>0.002</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.0004629629629629629</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>-0.001587301587301587</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>0.002</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.0004629629629629629</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>-0.001587301587301587</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>0.091</v>
+        <v>0.121</v>
       </c>
       <c r="V8">
-        <v>0.02106481481481481</v>
+        <v>0.03457142857142857</v>
+      </c>
+      <c r="W8">
+        <v>-0.1021929824561404</v>
       </c>
       <c r="X8">
-        <v>0.1092604807434712</v>
+        <v>0.1685207702050336</v>
+      </c>
+      <c r="Y8">
+        <v>-0.2707137526611739</v>
+      </c>
+      <c r="Z8">
+        <v>0.05945741563474808</v>
+      </c>
+      <c r="AA8">
+        <v>-0.08611399943283864</v>
       </c>
       <c r="AB8">
-        <v>0.09602839770682201</v>
+        <v>0.1538941059161559</v>
+      </c>
+      <c r="AC8">
+        <v>-0.2400081053489945</v>
       </c>
       <c r="AD8">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.55</v>
+        <v>1.03</v>
       </c>
       <c r="AG8">
-        <v>1.459</v>
+        <v>0.909</v>
       </c>
       <c r="AH8">
-        <v>0.2640545144804088</v>
+        <v>0.2273730684326711</v>
       </c>
       <c r="AI8">
-        <v>0.1452671040299906</v>
+        <v>0.1490593342981187</v>
       </c>
       <c r="AJ8">
-        <v>0.2524658245371172</v>
+        <v>0.2061691993649354</v>
       </c>
       <c r="AK8">
-        <v>0.1379147367426033</v>
+        <v>0.1338930623066726</v>
       </c>
       <c r="AL8">
-        <v>0.205</v>
+        <v>0.125</v>
       </c>
       <c r="AM8">
-        <v>0.205</v>
+        <v>0.125</v>
       </c>
       <c r="AN8">
-        <v>-1.359649122807018</v>
+        <v>-1.15990990990991</v>
       </c>
       <c r="AO8">
-        <v>-5.560975609756097</v>
+        <v>-7.288</v>
       </c>
       <c r="AP8">
-        <v>-1.279824561403509</v>
+        <v>-1.023648648648649</v>
       </c>
       <c r="AQ8">
-        <v>-5.560975609756097</v>
+        <v>-7.288</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cyan Limited (KASE:CYAN)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>-2.39</v>
+      </c>
+      <c r="M9">
+        <v>2.68</v>
+      </c>
+      <c r="N9">
+        <v>0.4802867383512545</v>
+      </c>
+      <c r="O9">
+        <v>-1.121338912133891</v>
+      </c>
+      <c r="P9">
+        <v>2.68</v>
+      </c>
+      <c r="Q9">
+        <v>0.4802867383512545</v>
+      </c>
+      <c r="R9">
+        <v>-1.121338912133891</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.014</v>
+      </c>
+      <c r="V9">
+        <v>0.002508960573476703</v>
+      </c>
+      <c r="W9">
+        <v>-0.1912</v>
+      </c>
+      <c r="X9">
+        <v>0.1671266044897337</v>
+      </c>
+      <c r="Y9">
+        <v>-0.3583266044897337</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>-0.1841953192718867</v>
+      </c>
+      <c r="AB9">
+        <v>0.1535143117884056</v>
+      </c>
+      <c r="AC9">
+        <v>-0.3377096310602923</v>
+      </c>
+      <c r="AD9">
+        <v>1.54</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>1.54</v>
+      </c>
+      <c r="AG9">
+        <v>1.526</v>
+      </c>
+      <c r="AH9">
+        <v>0.2162921348314607</v>
+      </c>
+      <c r="AI9">
+        <v>0.2067114093959732</v>
+      </c>
+      <c r="AJ9">
+        <v>0.2147481001970166</v>
+      </c>
+      <c r="AK9">
+        <v>0.2052178590640129</v>
+      </c>
+      <c r="AL9">
+        <v>0.287</v>
+      </c>
+      <c r="AM9">
+        <v>0.287</v>
+      </c>
+      <c r="AN9">
+        <v>-0.6039215686274511</v>
+      </c>
+      <c r="AO9">
+        <v>-8.885017421602788</v>
+      </c>
+      <c r="AP9">
+        <v>-0.5984313725490197</v>
+      </c>
+      <c r="AQ9">
+        <v>-8.885017421602788</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0394</v>
+        <v>0.1</v>
       </c>
       <c r="E2">
-        <v>-0.027</v>
+        <v>0.231</v>
       </c>
       <c r="G2">
-        <v>0.1718554078744671</v>
+        <v>0.01289532034076322</v>
       </c>
       <c r="H2">
-        <v>0.1718374950739799</v>
+        <v>0.01289532034076322</v>
       </c>
       <c r="I2">
-        <v>0.1048973596532082</v>
+        <v>0.1884117166530517</v>
       </c>
       <c r="J2">
-        <v>0.08397534695214923</v>
+        <v>0.145921867632622</v>
       </c>
       <c r="K2">
-        <v>4.528</v>
+        <v>2.67</v>
       </c>
       <c r="L2">
-        <v>0.08110916060616916</v>
+        <v>0.1557941416734741</v>
       </c>
       <c r="M2">
-        <v>4.376</v>
+        <v>1.846</v>
       </c>
       <c r="N2">
-        <v>0.1792487609060746</v>
+        <v>0.06831976313841599</v>
       </c>
       <c r="O2">
-        <v>0.9664310954063606</v>
+        <v>0.6913857677902622</v>
       </c>
       <c r="P2">
-        <v>4.376</v>
+        <v>1.846</v>
       </c>
       <c r="Q2">
-        <v>0.1792487609060746</v>
+        <v>0.06831976313841599</v>
       </c>
       <c r="R2">
-        <v>0.9664310954063606</v>
+        <v>0.6913857677902622</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.025</v>
+        <v>1.216</v>
       </c>
       <c r="V2">
-        <v>0.1239093925367632</v>
+        <v>0.04500370096225018</v>
       </c>
       <c r="W2">
-        <v>0.004411764705882353</v>
+        <v>0.0535907166836958</v>
       </c>
       <c r="X2">
-        <v>0.1479271621937633</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="Y2">
-        <v>-0.1435153974878809</v>
+        <v>-0.08347449795471884</v>
       </c>
       <c r="Z2">
-        <v>1.350966773951553</v>
+        <v>0.4763863794301599</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.03942546442367301</v>
       </c>
       <c r="AB2">
-        <v>0.1469033425597125</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="AC2">
-        <v>-0.1461009939540135</v>
+        <v>-0.1065647252758952</v>
       </c>
       <c r="AD2">
-        <v>8.863</v>
+        <v>5.914</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.863</v>
+        <v>5.914</v>
       </c>
       <c r="AG2">
-        <v>5.837999999999999</v>
+        <v>4.698</v>
       </c>
       <c r="AH2">
-        <v>0.2663481187642746</v>
+        <v>0.1795712637396004</v>
       </c>
       <c r="AI2">
-        <v>0.2065197129275794</v>
+        <v>0.1621251165085805</v>
       </c>
       <c r="AJ2">
-        <v>0.1929853558560047</v>
+        <v>0.14811778800681</v>
       </c>
       <c r="AK2">
-        <v>0.1463488004813115</v>
+        <v>0.1332312404287902</v>
       </c>
       <c r="AL2">
-        <v>0.448</v>
+        <v>0.2</v>
       </c>
       <c r="AM2">
-        <v>0.2919999999999999</v>
+        <v>0.194</v>
       </c>
       <c r="AN2">
-        <v>1.491083445491252</v>
+        <v>1.831526788479405</v>
       </c>
       <c r="AO2">
-        <v>13.07142857142857</v>
+        <v>16.145</v>
       </c>
       <c r="AP2">
-        <v>0.9821668909825032</v>
+        <v>1.454939609786311</v>
       </c>
       <c r="AQ2">
-        <v>20.05479452054795</v>
+        <v>16.64432989690722</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Globe Residency REIT (KASE:GRR)</t>
+          <t>MCB investment management Limited (KASE:MCBIM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,95 +721,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="E3">
+        <v>0.127</v>
+      </c>
       <c r="G3">
-        <v>0.1583665338645418</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="H3">
-        <v>0.1583665338645418</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="I3">
-        <v>0.1583665338645418</v>
+        <v>0.3492063492063492</v>
       </c>
       <c r="J3">
-        <v>0.1314815089086035</v>
+        <v>0.206530612244898</v>
       </c>
       <c r="K3">
-        <v>6.7</v>
+        <v>0.829</v>
       </c>
       <c r="L3">
-        <v>0.1334661354581673</v>
+        <v>0.2193121693121693</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.256</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03294723294723295</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.3088057901085646</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.256</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03294723294723295</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.3088057901085646</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.136</v>
+        <v>0.169</v>
       </c>
       <c r="V3">
-        <v>0.02048192771084338</v>
+        <v>0.02175032175032175</v>
       </c>
       <c r="X3">
-        <v>0.2164332403374553</v>
+        <v>0.139633262834615</v>
       </c>
       <c r="AB3">
-        <v>0.1638489810418891</v>
+        <v>0.1385580341584336</v>
       </c>
       <c r="AD3">
-        <v>6.13</v>
+        <v>0.286</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.13</v>
+        <v>0.286</v>
       </c>
       <c r="AG3">
-        <v>5.994</v>
+        <v>0.117</v>
       </c>
       <c r="AH3">
-        <v>0.4800313234142521</v>
+        <v>0.03550148957298908</v>
       </c>
       <c r="AI3">
-        <v>0.4588323353293413</v>
+        <v>0.0412936760034652</v>
       </c>
       <c r="AJ3">
-        <v>0.4744340668038626</v>
+        <v>0.01483453784709014</v>
       </c>
       <c r="AK3">
-        <v>0.4532667876588021</v>
+        <v>0.01731537664644072</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AM3">
-        <v>-0.147</v>
+        <v>0.025</v>
       </c>
       <c r="AN3">
-        <v>0.771069182389937</v>
+        <v>0.2166666666666666</v>
+      </c>
+      <c r="AO3">
+        <v>44.00000000000001</v>
       </c>
       <c r="AP3">
-        <v>0.7539622641509434</v>
+        <v>0.08863636363636361</v>
       </c>
       <c r="AQ3">
-        <v>-54.08163265306123</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCB-Arif Habib Savings and Investments Limited (KASE:MCBAH)</t>
+          <t>JS Investments Limited (KASE:JSIL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,121 +841,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0349</v>
+        <v>0.0499</v>
       </c>
       <c r="E4">
-        <v>-0.027</v>
+        <v>0.264</v>
       </c>
       <c r="G4">
-        <v>0.3759213759213759</v>
+        <v>-0.3325581395348837</v>
       </c>
       <c r="H4">
-        <v>0.3759213759213759</v>
+        <v>-0.3325581395348837</v>
       </c>
       <c r="I4">
-        <v>0.3292383292383292</v>
+        <v>0.3017441860465117</v>
       </c>
       <c r="J4">
-        <v>0.2000372273099546</v>
+        <v>0.2749224806201551</v>
       </c>
       <c r="K4">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="L4">
-        <v>0.1965601965601965</v>
+        <v>0.2616279069767442</v>
       </c>
       <c r="M4">
-        <v>1.5</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.2205882352941176</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>1.875</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>1.5</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.2205882352941176</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>1.875</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0.171</v>
+        <v>0.153</v>
       </c>
       <c r="V4">
-        <v>0.02514705882352941</v>
+        <v>0.04309859154929577</v>
       </c>
       <c r="W4">
-        <v>0.08179959100204499</v>
+        <v>0.07653061224489796</v>
       </c>
       <c r="X4">
-        <v>0.1479271621937633</v>
+        <v>0.1519622211775983</v>
       </c>
       <c r="Y4">
-        <v>-0.06612757119171826</v>
+        <v>-0.07543160893270037</v>
       </c>
       <c r="Z4">
-        <v>0.4377756265461978</v>
+        <v>0.253351008985123</v>
       </c>
       <c r="AA4">
-        <v>0.08757142251817956</v>
+        <v>0.06965188785780921</v>
       </c>
       <c r="AB4">
-        <v>0.1469033425597125</v>
+        <v>0.1451899628626813</v>
       </c>
       <c r="AC4">
-        <v>-0.05933192004153295</v>
+        <v>-0.07553807500487214</v>
       </c>
       <c r="AD4">
-        <v>0.163</v>
+        <v>0.758</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.163</v>
+        <v>0.758</v>
       </c>
       <c r="AG4">
-        <v>-0.008000000000000007</v>
+        <v>0.605</v>
       </c>
       <c r="AH4">
-        <v>0.02340944994973431</v>
+        <v>0.1759517177344475</v>
       </c>
       <c r="AI4">
-        <v>0.02406614498745017</v>
+        <v>0.1289554270159918</v>
       </c>
       <c r="AJ4">
-        <v>-0.001177856301531214</v>
+        <v>0.1456077015643803</v>
       </c>
       <c r="AK4">
-        <v>-0.001211754013935172</v>
+        <v>0.1056768558951965</v>
       </c>
       <c r="AL4">
-        <v>0.023</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AM4">
-        <v>0.017</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AN4">
-        <v>0.1164285714285714</v>
+        <v>1.460500963391137</v>
       </c>
       <c r="AO4">
-        <v>58.2608695652174</v>
+        <v>6.034883720930234</v>
       </c>
       <c r="AP4">
-        <v>-0.005714285714285719</v>
+        <v>1.165703275529865</v>
       </c>
       <c r="AQ4">
-        <v>78.82352941176471</v>
+        <v>6.034883720930234</v>
       </c>
     </row>
     <row r="5">
@@ -963,76 +972,73 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.268</v>
-      </c>
-      <c r="E5">
-        <v>-0.528</v>
+        <v>0.328</v>
       </c>
       <c r="G5">
-        <v>0.2323943661971831</v>
+        <v>0.3772455089820359</v>
       </c>
       <c r="H5">
-        <v>0.2323943661971831</v>
+        <v>0.3772455089820359</v>
       </c>
       <c r="I5">
-        <v>0.1901408450704226</v>
+        <v>0.3772455089820359</v>
       </c>
       <c r="J5">
-        <v>0.09507042253521128</v>
+        <v>0.2713520327765521</v>
       </c>
       <c r="K5">
+        <v>0.042</v>
+      </c>
+      <c r="L5">
+        <v>0.2514970059880239</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>0.006</v>
       </c>
-      <c r="L5">
-        <v>0.04225352112676057</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0.003</v>
-      </c>
       <c r="V5">
-        <v>0.00909090909090909</v>
+        <v>0.02054794520547945</v>
       </c>
       <c r="W5">
-        <v>0.004411764705882353</v>
+        <v>0.04117647058823529</v>
       </c>
       <c r="X5">
-        <v>0.1461009939540135</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="Y5">
-        <v>-0.1416892292481312</v>
+        <v>-0.09588874405017936</v>
       </c>
       <c r="Z5">
-        <v>0.1094834232845027</v>
+        <v>0.1642084562438545</v>
       </c>
       <c r="AA5">
-        <v>0.01040863531225906</v>
+        <v>0.04455829840086942</v>
       </c>
       <c r="AB5">
-        <v>0.1461009939540135</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="AC5">
-        <v>-0.1356923586417545</v>
+        <v>-0.09250691623754523</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1044,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1053,28 +1059,28 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.009174311926605505</v>
+        <v>-0.02097902097902098</v>
       </c>
       <c r="AK5">
-        <v>-0.002949852507374631</v>
+        <v>-0.007075471698113208</v>
       </c>
       <c r="AL5">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="AM5">
-        <v>0.009999999999999998</v>
+        <v>0.015</v>
       </c>
       <c r="AN5">
         <v>0</v>
       </c>
       <c r="AO5">
-        <v>2.076923076923077</v>
+        <v>3.9375</v>
       </c>
       <c r="AP5">
-        <v>-0.09375</v>
+        <v>-0.09230769230769231</v>
       </c>
       <c r="AQ5">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6">
@@ -1085,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sindh Modaraba (KASE:SINDM)</t>
+          <t>Cyan Limited (KASE:CYAN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1093,47 +1099,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.04389999999999999</v>
-      </c>
-      <c r="E6">
-        <v>0.174</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>-3.250950570342205</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>-3.250950570342205</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.7756653992395437</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.4847908745247148</v>
       </c>
       <c r="K6">
-        <v>0.345</v>
+        <v>0.2</v>
       </c>
       <c r="L6">
-        <v>0.4451612903225806</v>
+        <v>0.3802281368821293</v>
       </c>
       <c r="M6">
-        <v>0.196</v>
+        <v>0.003</v>
       </c>
       <c r="N6">
-        <v>0.1410071942446043</v>
+        <v>0.0004792332268370607</v>
       </c>
       <c r="O6">
-        <v>0.5681159420289855</v>
+        <v>0.015</v>
       </c>
       <c r="P6">
-        <v>0.196</v>
+        <v>0.003</v>
       </c>
       <c r="Q6">
-        <v>0.1410071942446043</v>
+        <v>0.0004792332268370607</v>
       </c>
       <c r="R6">
-        <v>0.5681159420289855</v>
+        <v>0.015</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1142,31 +1142,31 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2.58</v>
+        <v>0.019</v>
       </c>
       <c r="V6">
-        <v>1.856115107913669</v>
+        <v>0.003035143769968051</v>
       </c>
       <c r="W6">
-        <v>0.0368196371398079</v>
+        <v>0.0338409475465313</v>
       </c>
       <c r="X6">
-        <v>0.1461009939540135</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="Y6">
-        <v>-0.1092813568142056</v>
+        <v>-0.1032242670918833</v>
       </c>
       <c r="Z6">
-        <v>0.1266339869281046</v>
+        <v>0.07073695535233997</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.0342926304464766</v>
       </c>
       <c r="AB6">
-        <v>0.1461009939540135</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="AC6">
-        <v>-0.1461009939540135</v>
+        <v>-0.102772584191938</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-2.58</v>
+        <v>-0.019</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1187,16 +1187,28 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>2.168067226890756</v>
+        <v>-0.003044383912834482</v>
       </c>
       <c r="AK6">
-        <v>-0.5695364238410596</v>
+        <v>-0.003653143626225726</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.068</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>5.999999999999999</v>
+      </c>
+      <c r="AP6">
+        <v>-0.04691358024691358</v>
+      </c>
+      <c r="AQ6">
+        <v>5.999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unicap Modaraba (KASE:UCAPM)</t>
+          <t>Globe Residency REIT (KASE:GRR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,100 +1228,109 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.09384615384615384</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.09384615384615384</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.09282051282051282</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.06247281323877069</v>
       </c>
       <c r="K7">
-        <v>-0.001</v>
+        <v>0.954</v>
       </c>
       <c r="L7">
-        <v>-0.1</v>
+        <v>0.09784615384615385</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>1.4</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.467505241090147</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>1.4</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.467505241090147</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>0.003111111111111111</v>
       </c>
       <c r="W7">
-        <v>-0.005376344086021506</v>
+        <v>0.1319502074688796</v>
       </c>
       <c r="X7">
-        <v>0.1461009939540135</v>
+        <v>0.1874017528095623</v>
       </c>
       <c r="Y7">
-        <v>-0.151477338040035</v>
+        <v>-0.05545154534068261</v>
       </c>
       <c r="Z7">
-        <v>0.05376344086021505</v>
+        <v>0.7372958257713248</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.04606094442513719</v>
       </c>
       <c r="AB7">
-        <v>0.1461009939540135</v>
+        <v>0.1564178107849896</v>
       </c>
       <c r="AC7">
-        <v>-0.1461009939540135</v>
+        <v>-0.1103568663598524</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>4.849</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.419104991394148</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.4817012858555886</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>0.4180532804552117</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>0.4806224601050649</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>5.375275938189845</v>
+      </c>
+      <c r="AP7">
+        <v>5.352097130242826</v>
       </c>
     </row>
     <row r="8">
@@ -1320,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JS Investments Limited (KASE:JSIL)</t>
+          <t>Arpak International Investments Limited (KASE:ARPAK)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1329,25 +1350,25 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.219</v>
+        <v>0.1</v>
       </c>
       <c r="G8">
-        <v>-2.1939586645469</v>
+        <v>-0.07462686567164178</v>
       </c>
       <c r="H8">
-        <v>-2.1939586645469</v>
+        <v>-0.07462686567164178</v>
       </c>
       <c r="I8">
-        <v>-1.448330683624801</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="J8">
-        <v>-1.448330683624801</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="K8">
-        <v>-0.9320000000000001</v>
+        <v>-0.337</v>
       </c>
       <c r="L8">
-        <v>-1.481717011128776</v>
+        <v>-5.029850746268656</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1371,73 +1392,67 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.121</v>
+        <v>0.023</v>
       </c>
       <c r="V8">
-        <v>0.03457142857142857</v>
+        <v>0.02725118483412322</v>
       </c>
       <c r="W8">
-        <v>-0.1021929824561404</v>
+        <v>-0.2132911392405063</v>
       </c>
       <c r="X8">
-        <v>0.1685207702050336</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="Y8">
-        <v>-0.2707137526611739</v>
+        <v>-0.3503563538789209</v>
       </c>
       <c r="Z8">
-        <v>0.05945741563474808</v>
+        <v>0.04251269035532995</v>
       </c>
       <c r="AA8">
-        <v>-0.08611399943283864</v>
+        <v>0.008883248730964468</v>
       </c>
       <c r="AB8">
-        <v>0.1538941059161559</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="AC8">
-        <v>-0.2400081053489945</v>
+        <v>-0.1281819659074502</v>
       </c>
       <c r="AD8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>0.909</v>
+        <v>-0.023</v>
       </c>
       <c r="AH8">
-        <v>0.2273730684326711</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.1490593342981187</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.2061691993649354</v>
+        <v>-0.02801461632155908</v>
       </c>
       <c r="AK8">
-        <v>0.1338930623066726</v>
+        <v>-0.01773323053199691</v>
       </c>
       <c r="AL8">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>-1.15990990990991</v>
-      </c>
-      <c r="AO8">
-        <v>-7.288</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>-1.023648648648649</v>
-      </c>
-      <c r="AQ8">
-        <v>-7.288</v>
+        <v>-1.642857142857143</v>
       </c>
     </row>
     <row r="9">
@@ -1448,7 +1463,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cyan Limited (KASE:CYAN)</t>
+          <t>Sindh Modaraba (KASE:SINDM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1456,26 +1471,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.351</v>
+      </c>
+      <c r="E9">
+        <v>0.231</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
       <c r="K9">
-        <v>-2.39</v>
+        <v>0.532</v>
+      </c>
+      <c r="L9">
+        <v>0.475</v>
       </c>
       <c r="M9">
-        <v>2.68</v>
+        <v>0.187</v>
       </c>
       <c r="N9">
-        <v>0.4802867383512545</v>
+        <v>0.1375</v>
       </c>
       <c r="O9">
-        <v>-1.121338912133891</v>
+        <v>0.3515037593984962</v>
       </c>
       <c r="P9">
-        <v>2.68</v>
+        <v>0.187</v>
       </c>
       <c r="Q9">
-        <v>0.4802867383512545</v>
+        <v>0.1375</v>
       </c>
       <c r="R9">
-        <v>-1.121338912133891</v>
+        <v>0.3515037593984962</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1484,73 +1520,168 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.014</v>
+        <v>0.825</v>
       </c>
       <c r="V9">
-        <v>0.002508960573476703</v>
+        <v>0.6066176470588235</v>
       </c>
       <c r="W9">
-        <v>-0.1912</v>
+        <v>0.06600496277915632</v>
       </c>
       <c r="X9">
-        <v>0.1671266044897337</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="Y9">
-        <v>-0.3583266044897337</v>
+        <v>-0.07106025185925832</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>0.198581560283688</v>
       </c>
       <c r="AA9">
-        <v>-0.1841953192718867</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1535143117884056</v>
+        <v>0.1370652146384146</v>
       </c>
       <c r="AC9">
-        <v>-0.3377096310602923</v>
+        <v>-0.1370652146384146</v>
       </c>
       <c r="AD9">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>1.526</v>
+        <v>-0.825</v>
       </c>
       <c r="AH9">
-        <v>0.2162921348314607</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>0.2067114093959732</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0.2147481001970166</v>
+        <v>-1.542056074766355</v>
       </c>
       <c r="AK9">
-        <v>0.2052178590640129</v>
+        <v>-0.1600387972841901</v>
       </c>
       <c r="AL9">
-        <v>0.287</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>0.287</v>
-      </c>
-      <c r="AN9">
-        <v>-0.6039215686274511</v>
-      </c>
-      <c r="AO9">
-        <v>-8.885017421602788</v>
-      </c>
-      <c r="AP9">
-        <v>-0.5984313725490197</v>
-      </c>
-      <c r="AQ9">
-        <v>-8.885017421602788</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Unicap Modaraba (KASE:UCAPM)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0.1370652146384146</v>
+      </c>
+      <c r="Y10">
+        <v>-0.1370652146384146</v>
+      </c>
+      <c r="Z10">
+        <v>0.02730375426621161</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.1370652146384146</v>
+      </c>
+      <c r="AC10">
+        <v>-0.1370652146384146</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
